--- a/FPPN_PBC_complete_pointee_20261019.xlsx
+++ b/FPPN_PBC_complete_pointee_20261019.xlsx
@@ -975,7 +975,7 @@
     </row>
     <row r="7" ht="13.5" customHeight="1" s="48">
       <c r="M7" s="53">
-        <f>IFERROR(COUNTIF($M$11:$M$100,"Reçu")/(COUNTA($M$11:$M$100)-COUNTIF($M$11:$M$100,"Non Applicable")),0)</f>
+        <f>IFERROR(COUNTIF($M$11:$M$111,"Reçu")/(COUNTA($M$11:$M$111)-COUNTIF($M$11:$M$111,"Non Applicable")),0)</f>
         <v/>
       </c>
     </row>
@@ -3656,35 +3656,334 @@
     <row r="101" ht="13.5" customHeight="1" s="48">
       <c r="C101" s="67" t="n"/>
     </row>
-    <row r="102" ht="13.5" customHeight="1" s="48">
-      <c r="C102" s="67" t="n"/>
-    </row>
-    <row r="103" ht="13.5" customHeight="1" s="48">
-      <c r="C103" s="67" t="n"/>
-    </row>
-    <row r="104" ht="13.5" customHeight="1" s="48">
-      <c r="C104" s="67" t="n"/>
-    </row>
-    <row r="105" ht="13.5" customHeight="1" s="48">
-      <c r="C105" s="67" t="n"/>
-    </row>
-    <row r="106" ht="13.5" customHeight="1" s="48">
-      <c r="C106" s="67" t="n"/>
-    </row>
-    <row r="107" ht="13.5" customHeight="1" s="48">
-      <c r="C107" s="67" t="n"/>
-    </row>
-    <row r="108" ht="13.5" customHeight="1" s="48">
-      <c r="C108" s="67" t="n"/>
-    </row>
-    <row r="109" ht="13.5" customHeight="1" s="48">
-      <c r="C109" s="67" t="n"/>
-    </row>
-    <row r="110" ht="13.5" customHeight="1" s="48">
-      <c r="C110" s="67" t="n"/>
-    </row>
-    <row r="111" ht="13.5" customHeight="1" s="48">
-      <c r="C111" s="67" t="n"/>
+    <row r="102" ht="18" customHeight="1" s="48">
+      <c r="C102" s="69" t="inlineStr">
+        <is>
+          <t>Provisions et engagements (revue du rapport v5, 19/10/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="51" customHeight="1" s="48">
+      <c r="B103" s="70">
+        <f>+B100+1</f>
+        <v/>
+      </c>
+      <c r="C103" s="71" t="inlineStr">
+        <is>
+          <t>Bases des prestations maladie et décès sur le plus grand nombre d'années disponibles (au moins depuis 2019) jusqu'au 31/08/2026, une ligne par dossier : date de survenance (soins ou décès), date de déclaration, date de paiement, montant, statut (payé, en attente, rejeté). Nécessaires à la PSAP dossier par dossier et à la méthode CIMA des sinistres tardifs.</t>
+        </is>
+      </c>
+      <c r="E103" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G103" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H103" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I103" s="73" t="n"/>
+      <c r="J103" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K103" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M103" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1" s="48">
+      <c r="B104" s="70">
+        <f>+B103+1</f>
+        <v/>
+      </c>
+      <c r="C104" s="71" t="inlineStr">
+        <is>
+          <t>Note de calcul des provisions pour prestations à payer maladie et obsèques (comptes 15801000 et 15802000), liste des dossiers qui les composent, et raison de l'absence de mise à jour depuis 2020.</t>
+        </is>
+      </c>
+      <c r="E104" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G104" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H104" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I104" s="73" t="n"/>
+      <c r="J104" s="74" t="n"/>
+      <c r="K104" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M104" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1" s="48">
+      <c r="B105" s="70">
+        <f>+B104+1</f>
+        <v/>
+      </c>
+      <c r="C105" s="71" t="inlineStr">
+        <is>
+          <t>État des impayés du Grenier par tranche de retard au 31/12/2025 et au 31/08/2026, et politique de dépréciation des prêts en retard (décision, taux appliqués).</t>
+        </is>
+      </c>
+      <c r="E105" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G105" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H105" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I105" s="73" t="n"/>
+      <c r="J105" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K105" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M105" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="36" customHeight="1" s="48">
+      <c r="B106" s="70">
+        <f>+B105+1</f>
+        <v/>
+      </c>
+      <c r="C106" s="71" t="inlineStr">
+        <is>
+          <t>Politique de crédit et de recouvrement du Grenier : règles d'octroi, recouvrement des agents sortis ou non précomptés, traitement des prêts à mécano anormal.</t>
+        </is>
+      </c>
+      <c r="E106" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G106" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H106" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I106" s="73" t="n"/>
+      <c r="J106" s="74" t="n"/>
+      <c r="K106" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M106" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="36" customHeight="1" s="48">
+      <c r="B107" s="70">
+        <f>+B106+1</f>
+        <v/>
+      </c>
+      <c r="C107" s="71" t="inlineStr">
+        <is>
+          <t>Détail des mouvements du compte 47111106 « GNA ASSURANCE » de 2023 au 31/08/2026, avec les pièces justificatives.</t>
+        </is>
+      </c>
+      <c r="E107" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G107" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H107" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I107" s="73" t="n"/>
+      <c r="J107" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K107" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M107" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1" s="48">
+      <c r="B108" s="70">
+        <f>+B107+1</f>
+        <v/>
+      </c>
+      <c r="C108" s="71" t="inlineStr">
+        <is>
+          <t>Fichier du personnel du FPPN au 31/12/2025 et au 31/08/2026 : date de naissance, date d'embauche, salaire mensuel, catégorie, âge de départ prévu.</t>
+        </is>
+      </c>
+      <c r="E108" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G108" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H108" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I108" s="73" t="n"/>
+      <c r="J108" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K108" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M108" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1" s="48">
+      <c r="B109" s="70">
+        <f>+B108+1</f>
+        <v/>
+      </c>
+      <c r="C109" s="71" t="inlineStr">
+        <is>
+          <t>Convention collective et accord d'entreprise applicables au personnel du FPPN, articles fixant l'indemnité de départ à la retraite.</t>
+        </is>
+      </c>
+      <c r="E109" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G109" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H109" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I109" s="73" t="n"/>
+      <c r="J109" s="74" t="n"/>
+      <c r="K109" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M109" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="36" customHeight="1" s="48">
+      <c r="B110" s="70">
+        <f>+B109+1</f>
+        <v/>
+      </c>
+      <c r="C110" s="71" t="inlineStr">
+        <is>
+          <t>Note de calcul de la provision pour indemnités de départ à la retraite (compte 196) : méthode, hypothèses, liste des salariés.</t>
+        </is>
+      </c>
+      <c r="E110" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G110" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H110" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I110" s="73" t="n"/>
+      <c r="J110" s="74" t="n"/>
+      <c r="K110" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M110" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1" s="48">
+      <c r="B111" s="70">
+        <f>+B110+1</f>
+        <v/>
+      </c>
+      <c r="C111" s="71" t="inlineStr">
+        <is>
+          <t>Règles de la garantie santé des retraités : durée (à vie ou limitée), conditions, cotisation, décision qui la fonde.</t>
+        </is>
+      </c>
+      <c r="E111" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G111" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H111" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I111" s="73" t="n"/>
+      <c r="J111" s="74" t="n"/>
+      <c r="K111" s="75" t="inlineStr">
+        <is>
+          <t>Revue des provisions (rapport v5) : analyse en attente de ce document.</t>
+        </is>
+      </c>
+      <c r="M111" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="13.5" customHeight="1" s="48">
       <c r="C112" s="67" t="n"/>
@@ -3770,15 +4069,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E11:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="E11:E111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Urgent,Moyen,Faible"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="J11:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J11:J111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Physique,Electronique,Physique et Electronique"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="M11:M100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="M11:M111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Reçu,Non Reçu,Non Applicable,Partiellement Reçu"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3850,7 +4149,7 @@
         </is>
       </c>
       <c r="C6" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$100,"Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$111,"Reçu")</f>
         <v/>
       </c>
       <c r="D6" s="95" t="n"/>
@@ -3862,7 +4161,7 @@
         </is>
       </c>
       <c r="C7" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$100,"Partiellement Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$111,"Partiellement Reçu")</f>
         <v/>
       </c>
       <c r="D7" s="95" t="inlineStr">
@@ -3878,12 +4177,12 @@
         </is>
       </c>
       <c r="C8" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$100,"Non Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$111,"Non Reçu")</f>
         <v/>
       </c>
       <c r="D8" s="95" t="inlineStr">
         <is>
-          <t>1, 2, 5, 7, 8, 10, 11, 13, 14, 15, 16, 18, 19, 20, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 38, 39, 40, 41, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70</t>
+          <t>1, 2, 5, 7, 8, 10, 11, 13, 14, 15, 16, 18, 19, 20, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 38, 39, 40, 41, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79</t>
         </is>
       </c>
     </row>
@@ -3899,7 +4198,7 @@
       </c>
       <c r="D9" s="95" t="inlineStr">
         <is>
-          <t>1 à 70</t>
+          <t>1 à 79</t>
         </is>
       </c>
     </row>
@@ -41169,7 +41468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:E34"/>
+  <dimension ref="B2:E37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="2" customWidth="1" style="77" min="1" max="1"/>
@@ -41810,6 +42109,66 @@
         </is>
       </c>
     </row>
+    <row r="35" s="48">
+      <c r="B35" s="94" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" s="95" t="inlineStr">
+        <is>
+          <t>Provisions figées</t>
+        </is>
+      </c>
+      <c r="D35" s="95" t="inlineStr">
+        <is>
+          <t>Les provisions maladie et obsèques ont le même montant de 2020 au 31/08/2026, sans dotation ni reprise (comptes 6901, 7901 absents).</t>
+        </is>
+      </c>
+      <c r="E35" s="95" t="inlineStr">
+        <is>
+          <t>Transmettre la note de calcul et la liste des dossiers (item 72).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" s="48">
+      <c r="B36" s="94" t="n">
+        <v>31</v>
+      </c>
+      <c r="C36" s="95" t="inlineStr">
+        <is>
+          <t>Compte GNA 47111106</t>
+        </is>
+      </c>
+      <c r="D36" s="95" t="inlineStr">
+        <is>
+          <t>Compte mouvementé au débit depuis 2023, alors que les primes vont directement à GNA selon l'entretien du 19/10/2026.</t>
+        </is>
+      </c>
+      <c r="E36" s="95" t="inlineStr">
+        <is>
+          <t>Expliquer la nature des mouvements (item 75).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" s="48">
+      <c r="B37" s="94" t="n">
+        <v>32</v>
+      </c>
+      <c r="C37" s="95" t="inlineStr">
+        <is>
+          <t>Provision pour départ à la retraite</t>
+        </is>
+      </c>
+      <c r="D37" s="95" t="inlineStr">
+        <is>
+          <t>Provision reprise et dotée en totalité chaque année, méthode non communiquée.</t>
+        </is>
+      </c>
+      <c r="E37" s="95" t="inlineStr">
+        <is>
+          <t>Transmettre la note de calcul et le fichier du personnel (items 76 à 78).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/FPPN_PBC_complete_pointee_20261019.xlsx
+++ b/FPPN_PBC_complete_pointee_20261019.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:M129"/>
+  <dimension ref="B4:M135"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.18359375" defaultRowHeight="13.5" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.82" customWidth="1" style="44" min="1" max="1"/>
@@ -975,7 +975,7 @@
     </row>
     <row r="7" ht="13.5" customHeight="1" s="48">
       <c r="M7" s="53">
-        <f>IFERROR(COUNTIF($M$11:$M$111,"Reçu")/(COUNTA($M$11:$M$111)-COUNTIF($M$11:$M$111,"Non Applicable")),0)</f>
+        <f>IFERROR(COUNTIF($M$11:$M$135,"Reçu")/(COUNTA($M$11:$M$135)-COUNTIF($M$11:$M$135,"Non Applicable")),0)</f>
         <v/>
       </c>
     </row>
@@ -3988,56 +3988,738 @@
     <row r="112" ht="13.5" customHeight="1" s="48">
       <c r="C112" s="67" t="n"/>
     </row>
-    <row r="113" ht="13.5" customHeight="1" s="48">
-      <c r="C113" s="67" t="n"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1" s="48">
-      <c r="C114" s="67" t="n"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1" s="48">
-      <c r="C115" s="67" t="n"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1" s="48">
-      <c r="C116" s="67" t="n"/>
-    </row>
-    <row r="117" ht="13.5" customHeight="1" s="48">
-      <c r="C117" s="67" t="n"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1" s="48">
-      <c r="C118" s="67" t="n"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1" s="48">
-      <c r="C119" s="67" t="n"/>
-    </row>
-    <row r="120" ht="13.5" customHeight="1" s="48">
-      <c r="C120" s="67" t="n"/>
-    </row>
-    <row r="121" ht="13.5" customHeight="1" s="48">
-      <c r="C121" s="67" t="n"/>
-    </row>
-    <row r="122" ht="13.5" customHeight="1" s="48">
-      <c r="C122" s="67" t="n"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1" s="48">
-      <c r="C123" s="67" t="n"/>
-    </row>
-    <row r="124" ht="13.5" customHeight="1" s="48">
-      <c r="C124" s="67" t="n"/>
-    </row>
-    <row r="125" ht="13.5" customHeight="1" s="48">
-      <c r="C125" s="67" t="n"/>
+    <row r="113" ht="18" customHeight="1" s="48">
+      <c r="C113" s="69" t="inlineStr">
+        <is>
+          <t>Placements et autres actifs (entretiens du 19/10/2026, 14h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="21" customHeight="1" s="48">
+      <c r="B114" s="70">
+        <f>+B111+1</f>
+        <v/>
+      </c>
+      <c r="C114" s="71" t="inlineStr">
+        <is>
+          <t>Conventions, taux, échéances et relevés du DAT BOA (compte 52210200) de 2020 au 31/08/2026.</t>
+        </is>
+      </c>
+      <c r="E114" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G114" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H114" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I114" s="73" t="n"/>
+      <c r="J114" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K114" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M114" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="36" customHeight="1" s="48">
+      <c r="B115" s="70">
+        <f>+B114+1</f>
+        <v/>
+      </c>
+      <c r="C115" s="71" t="inlineStr">
+        <is>
+          <t>Bulletin de souscription au FCP géré par United Capital (SGI), valeurs liquidatives et relevés de 2025 au 31/08/2026.</t>
+        </is>
+      </c>
+      <c r="E115" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G115" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H115" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I115" s="73" t="n"/>
+      <c r="J115" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K115" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M115" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="36" customHeight="1" s="48">
+      <c r="B116" s="70">
+        <f>+B115+1</f>
+        <v/>
+      </c>
+      <c r="C116" s="71" t="inlineStr">
+        <is>
+          <t>Inventaire et tableau de variation de tous les placements de 2016 au 31/08/2026 : souscriptions, intérêts, débouclages, par banque ou gestionnaire.</t>
+        </is>
+      </c>
+      <c r="E116" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G116" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H116" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I116" s="73" t="n"/>
+      <c r="J116" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K116" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M116" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="21" customHeight="1" s="48">
+      <c r="B117" s="70">
+        <f>+B116+1</f>
+        <v/>
+      </c>
+      <c r="C117" s="71" t="inlineStr">
+        <is>
+          <t>Correspondance avec Orabank sur l'arrêt des prélèvements mensuels et le remboursement du DAT.</t>
+        </is>
+      </c>
+      <c r="E117" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G117" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H117" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I117" s="73" t="n"/>
+      <c r="J117" s="74" t="n"/>
+      <c r="K117" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M117" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="36" customHeight="1" s="48">
+      <c r="B118" s="70">
+        <f>+B117+1</f>
+        <v/>
+      </c>
+      <c r="C118" s="71" t="inlineStr">
+        <is>
+          <t>Titres de propriété ou actes d'acquisition des terrains, situation de chaque terrain (projet, attribution, litige).</t>
+        </is>
+      </c>
+      <c r="E118" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G118" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H118" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I118" s="73" t="n"/>
+      <c r="J118" s="74" t="n"/>
+      <c r="K118" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M118" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="21" customHeight="1" s="48">
+      <c r="B119" s="70">
+        <f>+B118+1</f>
+        <v/>
+      </c>
+      <c r="C119" s="71" t="inlineStr">
+        <is>
+          <t>Baux et encaissements des immeubles d'Aboisso.</t>
+        </is>
+      </c>
+      <c r="E119" s="72" t="inlineStr">
+        <is>
+          <t>Faible</t>
+        </is>
+      </c>
+      <c r="G119" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H119" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I119" s="73" t="n"/>
+      <c r="J119" s="74" t="n"/>
+      <c r="K119" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M119" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="21" customHeight="1" s="48">
+      <c r="B120" s="70">
+        <f>+B119+1</f>
+        <v/>
+      </c>
+      <c r="C120" s="71" t="inlineStr">
+        <is>
+          <t>Rapport de réévaluation du siège et décision de comptabilisation au compte 10620000.</t>
+        </is>
+      </c>
+      <c r="E120" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G120" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H120" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I120" s="73" t="n"/>
+      <c r="J120" s="74" t="n"/>
+      <c r="K120" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M120" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1" s="48">
+      <c r="B121" s="70">
+        <f>+B120+1</f>
+        <v/>
+      </c>
+      <c r="C121" s="71" t="inlineStr">
+        <is>
+          <t>Dossier de la créance sur l'hôpital de la Police (compte 47111100) : pièces, correspondances avec l'État, décision d'autonomie de l'hôpital.</t>
+        </is>
+      </c>
+      <c r="E121" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G121" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H121" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I121" s="73" t="n"/>
+      <c r="J121" s="74" t="n"/>
+      <c r="K121" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M121" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="21" customHeight="1" s="48">
+      <c r="B122" s="70">
+        <f>+B121+1</f>
+        <v/>
+      </c>
+      <c r="C122" s="71" t="inlineStr">
+        <is>
+          <t>Bilan d'ouverture de la clinique du FPPN (CMP) et détail des comptes 47111104 et 47111105.</t>
+        </is>
+      </c>
+      <c r="E122" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G122" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H122" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I122" s="73" t="n"/>
+      <c r="J122" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K122" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M122" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="21" customHeight="1" s="48">
+      <c r="B123" s="70">
+        <f>+B122+1</f>
+        <v/>
+      </c>
+      <c r="C123" s="71" t="inlineStr">
+        <is>
+          <t>Convention d'apporteur d'affaires avec GNA et décomptes annuels des commissions (20 % des primes collectées).</t>
+        </is>
+      </c>
+      <c r="E123" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G123" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H123" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I123" s="73" t="n"/>
+      <c r="J123" s="74" t="n"/>
+      <c r="K123" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M123" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="21" customHeight="1" s="48">
+      <c r="B124" s="70">
+        <f>+B123+1</f>
+        <v/>
+      </c>
+      <c r="C124" s="71" t="inlineStr">
+        <is>
+          <t>Liste des comptes bancaires, actifs et inactifs, avec leurs signataires.</t>
+        </is>
+      </c>
+      <c r="E124" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G124" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H124" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I124" s="73" t="n"/>
+      <c r="J124" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K124" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M124" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="21" customHeight="1" s="48">
+      <c r="B125" s="70">
+        <f>+B124+1</f>
+        <v/>
+      </c>
+      <c r="C125" s="71" t="inlineStr">
+        <is>
+          <t>État des chèques en suspens et des chèques annulés lors des changements de signataires.</t>
+        </is>
+      </c>
+      <c r="E125" s="72" t="inlineStr">
+        <is>
+          <t>Faible</t>
+        </is>
+      </c>
+      <c r="G125" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H125" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I125" s="73" t="n"/>
+      <c r="J125" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K125" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M125" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="13.5" customHeight="1" s="48">
       <c r="C126" s="67" t="n"/>
     </row>
-    <row r="127" ht="13.5" customHeight="1" s="48">
-      <c r="C127" s="67" t="n"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1" s="48">
-      <c r="C128" s="67" t="n"/>
-    </row>
-    <row r="129" ht="13.5" customHeight="1" s="48">
-      <c r="C129" s="67" t="n"/>
+    <row r="127" ht="18" customHeight="1" s="48">
+      <c r="C127" s="69" t="inlineStr">
+        <is>
+          <t>Provisions (entretiens du 19/10/2026, 16h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="36" customHeight="1" s="48">
+      <c r="B128" s="70">
+        <f>+B125+1</f>
+        <v/>
+      </c>
+      <c r="C128" s="71" t="inlineStr">
+        <is>
+          <t>Fichiers des décès transmis par la direction du personnel et calcul de fin d'année des allocations restant à payer, de 2020 à 2025, avec le compte utilisé.</t>
+        </is>
+      </c>
+      <c r="E128" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G128" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H128" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I128" s="73" t="n"/>
+      <c r="J128" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K128" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M128" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="21" customHeight="1" s="48">
+      <c r="B129" s="70">
+        <f>+B128+1</f>
+        <v/>
+      </c>
+      <c r="C129" s="71" t="inlineStr">
+        <is>
+          <t>Barème officiel des allocations décès par grade (sous-officier, officier, commissaire).</t>
+        </is>
+      </c>
+      <c r="E129" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G129" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H129" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I129" s="73" t="n"/>
+      <c r="J129" s="74" t="n"/>
+      <c r="K129" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M129" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="21" customHeight="1" s="48">
+      <c r="B130" s="70">
+        <f>+B129+1</f>
+        <v/>
+      </c>
+      <c r="C130" s="71" t="inlineStr">
+        <is>
+          <t>Contrats et décomptes de gestion de la garantie décès avec LMAI et Sanlam.</t>
+        </is>
+      </c>
+      <c r="E130" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G130" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H130" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I130" s="73" t="n"/>
+      <c r="J130" s="74" t="n"/>
+      <c r="K130" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M130" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="21" customHeight="1" s="48">
+      <c r="B131" s="70">
+        <f>+B130+1</f>
+        <v/>
+      </c>
+      <c r="C131" s="71" t="inlineStr">
+        <is>
+          <t>Courrier de l'AIRMS demandant le reclassement des provisions en compte 158.</t>
+        </is>
+      </c>
+      <c r="E131" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G131" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H131" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I131" s="73" t="n"/>
+      <c r="J131" s="74" t="n"/>
+      <c r="K131" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M131" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="21" customHeight="1" s="48">
+      <c r="B132" s="70">
+        <f>+B131+1</f>
+        <v/>
+      </c>
+      <c r="C132" s="71" t="inlineStr">
+        <is>
+          <t>Notification du taux de risques professionnels (2 %) par la CNPS.</t>
+        </is>
+      </c>
+      <c r="E132" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G132" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H132" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I132" s="73" t="n"/>
+      <c r="J132" s="74" t="n"/>
+      <c r="K132" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M132" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="21" customHeight="1" s="48">
+      <c r="B133" s="70">
+        <f>+B132+1</f>
+        <v/>
+      </c>
+      <c r="C133" s="71" t="inlineStr">
+        <is>
+          <t>Déclarations CNPS de 2020 au 31/08/2026.</t>
+        </is>
+      </c>
+      <c r="E133" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G133" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H133" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I133" s="73" t="n"/>
+      <c r="J133" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K133" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M133" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="21" customHeight="1" s="48">
+      <c r="B134" s="70">
+        <f>+B133+1</f>
+        <v/>
+      </c>
+      <c r="C134" s="71" t="inlineStr">
+        <is>
+          <t>Fichiers de calcul de la provision pour départ à la retraite de 2020 à 2026 (complète l'item 78).</t>
+        </is>
+      </c>
+      <c r="E134" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G134" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H134" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I134" s="73" t="n"/>
+      <c r="J134" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K134" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M134" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="21" customHeight="1" s="48">
+      <c r="B135" s="70">
+        <f>+B134+1</f>
+        <v/>
+      </c>
+      <c r="C135" s="71" t="inlineStr">
+        <is>
+          <t>Décision fixant le taux servi de 3,5 % sur le PEP et l'EFC.</t>
+        </is>
+      </c>
+      <c r="E135" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G135" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H135" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I135" s="73" t="n"/>
+      <c r="J135" s="74" t="n"/>
+      <c r="K135" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue des entretiens du 19/10/2026 avec le chef comptable (PBC complémentaire placements et provisions).</t>
+        </is>
+      </c>
+      <c r="M135" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B12:P12"/>
@@ -4069,15 +4751,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E11:E111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="E11:E135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Urgent,Moyen,Faible"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="J11:J111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J11:J135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Physique,Electronique,Physique et Electronique"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="M11:M111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="M11:M135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Reçu,Non Reçu,Non Applicable,Partiellement Reçu"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4149,7 +4831,7 @@
         </is>
       </c>
       <c r="C6" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$111,"Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$135,"Reçu")</f>
         <v/>
       </c>
       <c r="D6" s="95" t="n"/>
@@ -4161,7 +4843,7 @@
         </is>
       </c>
       <c r="C7" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$111,"Partiellement Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$135,"Partiellement Reçu")</f>
         <v/>
       </c>
       <c r="D7" s="95" t="inlineStr">
@@ -4177,12 +4859,12 @@
         </is>
       </c>
       <c r="C8" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$111,"Non Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$135,"Non Reçu")</f>
         <v/>
       </c>
       <c r="D8" s="95" t="inlineStr">
         <is>
-          <t>1, 2, 5, 7, 8, 10, 11, 13, 14, 15, 16, 18, 19, 20, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 38, 39, 40, 41, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79</t>
+          <t>1, 2, 5, 7, 8, 10, 11, 13, 14, 15, 16, 18, 19, 20, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 38, 39, 40, 41, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4880,7 @@
       </c>
       <c r="D9" s="95" t="inlineStr">
         <is>
-          <t>1 à 79</t>
+          <t>1 à 99</t>
         </is>
       </c>
     </row>
@@ -41468,7 +42150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:E37"/>
+  <dimension ref="B2:E42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="2" customWidth="1" style="77" min="1" max="1"/>
@@ -42169,6 +42851,106 @@
         </is>
       </c>
     </row>
+    <row r="38" s="48">
+      <c r="B38" s="94" t="n">
+        <v>33</v>
+      </c>
+      <c r="C38" s="95" t="inlineStr">
+        <is>
+          <t>DAT BOA</t>
+        </is>
+      </c>
+      <c r="D38" s="95" t="inlineStr">
+        <is>
+          <t>Le chef comptable le décrit comme un placement du FPPN qui sert aussi à payer l'EFC ; le compte s'intitule « DAT BOA Entraide fin de carrière ».</t>
+        </is>
+      </c>
+      <c r="E38" s="95" t="inlineStr">
+        <is>
+          <t>Confirmer la nature et l'affectation du DAT (item 80).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" s="48">
+      <c r="B39" s="94" t="n">
+        <v>34</v>
+      </c>
+      <c r="C39" s="95" t="inlineStr">
+        <is>
+          <t>Compte 10620000</t>
+        </is>
+      </c>
+      <c r="D39" s="95" t="inlineStr">
+        <is>
+          <t>Réévaluation du terrain du siège selon le chef comptable ; l'intitulé du compte parle de matériels.</t>
+        </is>
+      </c>
+      <c r="E39" s="95" t="inlineStr">
+        <is>
+          <t>Transmettre le rapport de réévaluation (item 86).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" s="48">
+      <c r="B40" s="94" t="n">
+        <v>35</v>
+      </c>
+      <c r="C40" s="95" t="inlineStr">
+        <is>
+          <t>Commissions GNA</t>
+        </is>
+      </c>
+      <c r="D40" s="95" t="inlineStr">
+        <is>
+          <t>Commission déclarée de 20 % des primes collectées ; en 2024, la commission comptabilisée ne vaut pas 20 % des précomptes 9W3.</t>
+        </is>
+      </c>
+      <c r="E40" s="95" t="inlineStr">
+        <is>
+          <t>Transmettre la convention et les décomptes (item 89).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" s="48">
+      <c r="B41" s="94" t="n">
+        <v>36</v>
+      </c>
+      <c r="C41" s="95" t="inlineStr">
+        <is>
+          <t>Allocations décès</t>
+        </is>
+      </c>
+      <c r="D41" s="95" t="inlineStr">
+        <is>
+          <t>Calcul de fin d'année des allocations restant à payer ; compte de comptabilisation non précisé.</t>
+        </is>
+      </c>
+      <c r="E41" s="95" t="inlineStr">
+        <is>
+          <t>Indiquer le compte et transmettre les calculs (item 92).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" s="48">
+      <c r="B42" s="94" t="n">
+        <v>37</v>
+      </c>
+      <c r="C42" s="95" t="inlineStr">
+        <is>
+          <t>Barème décès des officiers</t>
+        </is>
+      </c>
+      <c r="D42" s="95" t="inlineStr">
+        <is>
+          <t>Montant de l'allocation des officiers non confirmé.</t>
+        </is>
+      </c>
+      <c r="E42" s="95" t="inlineStr">
+        <is>
+          <t>Transmettre le barème (item 93).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/FPPN_PBC_complete_pointee_20261019.xlsx
+++ b/FPPN_PBC_complete_pointee_20261019.xlsx
@@ -17,8 +17,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PBC Actuariat FPPN'!$B$12:$P$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'PBC Actuariat FPPN'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'PBC Actuariat FPPN'!$A$1:$N$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'PBC Actuariat FPPN'!$A$1:$N$136</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Synthèse du pointage'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Synthèse du pointage'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Détail par mois'!$B$5:$E$1605</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Points à clarifier'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Points à clarifier'!$A$1:$E$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -281,7 +285,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -567,6 +571,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1073,7 +1080,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="61.5" customHeight="1" s="48">
+    <row r="12" ht="72" customHeight="1" s="48">
       <c r="B12" s="70">
         <f>+B11+1</f>
         <v/>
@@ -1107,7 +1114,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="117.75" customHeight="1" s="48">
+    <row r="13" ht="132" customHeight="1" s="48">
       <c r="B13" s="70">
         <f>+B12+1</f>
         <v/>
@@ -1143,7 +1150,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="132" customHeight="1" s="48">
+    <row r="14" ht="147" customHeight="1" s="48">
       <c r="B14" s="70">
         <f>+B13+1</f>
         <v/>
@@ -1179,7 +1186,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1" s="48">
+    <row r="15" ht="57" customHeight="1" s="48">
       <c r="B15" s="70">
         <f>+B14+1</f>
         <v/>
@@ -1223,7 +1230,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="117.75" customHeight="1" s="48">
+    <row r="18" ht="132" customHeight="1" s="48">
       <c r="B18" s="70">
         <f>+B15+1</f>
         <v/>
@@ -1259,7 +1266,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="33.75" customHeight="1" s="48">
+    <row r="19" ht="42" customHeight="1" s="48">
       <c r="B19" s="70">
         <f>+B18+1</f>
         <v/>
@@ -1293,7 +1300,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="33.75" customHeight="1" s="48">
+    <row r="20" ht="42" customHeight="1" s="48">
       <c r="B20" s="70">
         <f>+B19+1</f>
         <v/>
@@ -1377,7 +1384,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="33.75" customHeight="1" s="48">
+    <row r="24" ht="42" customHeight="1" s="48">
       <c r="B24" s="70">
         <f>+B23+1</f>
         <v/>
@@ -1453,7 +1460,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="159.75" customHeight="1" s="48">
+    <row r="26" ht="162" customHeight="1" s="48">
       <c r="B26" s="70">
         <f>+B25+1</f>
         <v/>
@@ -1503,7 +1510,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="61.5" customHeight="1" s="48">
+    <row r="29" ht="72" customHeight="1" s="48">
       <c r="B29" s="70">
         <f>+B26+1</f>
         <v/>
@@ -1541,7 +1548,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="75.75" customHeight="1" s="48">
+    <row r="30" ht="87" customHeight="1" s="48">
       <c r="B30" s="70">
         <f>+B29+1</f>
         <v/>
@@ -1579,7 +1586,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="33.75" customHeight="1" s="48">
+    <row r="31" ht="42" customHeight="1" s="48">
       <c r="B31" s="70">
         <f>+B30+1</f>
         <v/>
@@ -1627,7 +1634,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="48" customHeight="1" s="48">
+    <row r="34" ht="57" customHeight="1" s="48">
       <c r="B34" s="70">
         <f>+B31+1</f>
         <v/>
@@ -1661,7 +1668,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="103.5" customHeight="1" s="48">
+    <row r="35" ht="117" customHeight="1" s="48">
       <c r="B35" s="70">
         <f>+B34+1</f>
         <v/>
@@ -1783,7 +1790,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="33.75" customHeight="1" s="48">
+    <row r="40" ht="42" customHeight="1" s="48">
       <c r="B40" s="70">
         <f>+B37+1</f>
         <v/>
@@ -1821,7 +1828,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="117.75" customHeight="1" s="48">
+    <row r="41" ht="132" customHeight="1" s="48">
       <c r="B41" s="70">
         <f>+B40+1</f>
         <v/>
@@ -1861,7 +1868,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="33.75" customHeight="1" s="48">
+    <row r="42" ht="42" customHeight="1" s="48">
       <c r="B42" s="70">
         <f>+B41+1</f>
         <v/>
@@ -1895,7 +1902,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="48" customHeight="1" s="48">
+    <row r="43" ht="57" customHeight="1" s="48">
       <c r="B43" s="70">
         <f>+B42+1</f>
         <v/>
@@ -1973,7 +1980,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="33.75" customHeight="1" s="48">
+    <row r="47" ht="42" customHeight="1" s="48">
       <c r="B47" s="70">
         <f>+B44+1</f>
         <v/>
@@ -2007,7 +2014,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="33.75" customHeight="1" s="48">
+    <row r="48" ht="42" customHeight="1" s="48">
       <c r="B48" s="70">
         <f>+B47+1</f>
         <v/>
@@ -2051,7 +2058,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="33.75" customHeight="1" s="48">
+    <row r="51" ht="42" customHeight="1" s="48">
       <c r="B51" s="70">
         <f>+B48+1</f>
         <v/>
@@ -2089,7 +2096,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="61.5" customHeight="1" s="48">
+    <row r="52" ht="72" customHeight="1" s="48">
       <c r="B52" s="70">
         <f>+B51+1</f>
         <v/>
@@ -2127,7 +2134,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="48" customHeight="1" s="48">
+    <row r="53" ht="57" customHeight="1" s="48">
       <c r="B53" s="70">
         <f>+B52+1</f>
         <v/>
@@ -2165,7 +2172,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="33.75" customFormat="1" customHeight="1" s="68">
+    <row r="54" ht="42" customFormat="1" customHeight="1" s="68">
       <c r="B54" s="70">
         <f>+B53+1</f>
         <v/>
@@ -2199,7 +2206,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="33.75" customHeight="1" s="48">
+    <row r="55" ht="42" customHeight="1" s="48">
       <c r="B55" s="70">
         <f>+B54+1</f>
         <v/>
@@ -2237,7 +2244,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="33.75" customHeight="1" s="48">
+    <row r="56" ht="42" customHeight="1" s="48">
       <c r="B56" s="70">
         <f>+B55+1</f>
         <v/>
@@ -2271,7 +2278,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="33.75" customHeight="1" s="48">
+    <row r="57" ht="42" customHeight="1" s="48">
       <c r="B57" s="70">
         <f>+B56+1</f>
         <v/>
@@ -2305,7 +2312,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="33.75" customHeight="1" s="48">
+    <row r="58" ht="42" customHeight="1" s="48">
       <c r="B58" s="70">
         <f>+B57+1</f>
         <v/>
@@ -2373,7 +2380,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="33.75" customHeight="1" s="48">
+    <row r="60" ht="42" customHeight="1" s="48">
       <c r="B60" s="70">
         <f>+B59+1</f>
         <v/>
@@ -2481,7 +2488,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="33.75" customHeight="1" s="48">
+    <row r="63" ht="42" customHeight="1" s="48">
       <c r="B63" s="70">
         <f>+B62+1</f>
         <v/>
@@ -2525,7 +2532,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="61.5" customHeight="1" s="48">
+    <row r="66" ht="72" customHeight="1" s="48">
       <c r="B66" s="70">
         <f>+B63+1</f>
         <v/>
@@ -2563,7 +2570,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="33.75" customHeight="1" s="48">
+    <row r="67" ht="42" customHeight="1" s="48">
       <c r="B67" s="70">
         <f>+B66+1</f>
         <v/>
@@ -2637,7 +2644,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="33.75" customHeight="1" s="48">
+    <row r="69" ht="42" customHeight="1" s="48">
       <c r="B69" s="70">
         <f>+B68+1</f>
         <v/>
@@ -2685,7 +2692,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="33.75" customHeight="1" s="48">
+    <row r="72" ht="42" customHeight="1" s="48">
       <c r="B72" s="70">
         <f>+B69+1</f>
         <v/>
@@ -2719,7 +2726,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="33.75" customHeight="1" s="48">
+    <row r="73" ht="42" customHeight="1" s="48">
       <c r="B73" s="70">
         <f>+B72+1</f>
         <v/>
@@ -2753,7 +2760,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="33.75" customHeight="1" s="48">
+    <row r="74" ht="42" customHeight="1" s="48">
       <c r="B74" s="70">
         <f>+B73+1</f>
         <v/>
@@ -2787,7 +2794,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="33.75" customHeight="1" s="48">
+    <row r="75" ht="42" customHeight="1" s="48">
       <c r="B75" s="70">
         <f>+B74+1</f>
         <v/>
@@ -2821,7 +2828,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="33.75" customHeight="1" s="48">
+    <row r="76" ht="42" customHeight="1" s="48">
       <c r="B76" s="70">
         <f>+B75+1</f>
         <v/>
@@ -2855,7 +2862,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="33.75" customHeight="1" s="48">
+    <row r="77" ht="42" customHeight="1" s="48">
       <c r="B77" s="70">
         <f>+B76+1</f>
         <v/>
@@ -2889,7 +2896,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="33.75" customHeight="1" s="48">
+    <row r="78" ht="42" customHeight="1" s="48">
       <c r="B78" s="70">
         <f>+B77+1</f>
         <v/>
@@ -2923,7 +2930,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="33.75" customHeight="1" s="48">
+    <row r="79" ht="42" customHeight="1" s="48">
       <c r="B79" s="70">
         <f>+B78+1</f>
         <v/>
@@ -2957,7 +2964,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="33.75" customHeight="1" s="48">
+    <row r="80" ht="42" customHeight="1" s="48">
       <c r="B80" s="70">
         <f>+B79+1</f>
         <v/>
@@ -2991,7 +2998,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="33.75" customHeight="1" s="48">
+    <row r="81" ht="42" customHeight="1" s="48">
       <c r="B81" s="70">
         <f>+B80+1</f>
         <v/>
@@ -3025,7 +3032,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="33.75" customHeight="1" s="48">
+    <row r="82" ht="42" customHeight="1" s="48">
       <c r="B82" s="70">
         <f>+B81+1</f>
         <v/>
@@ -3059,7 +3066,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="33.75" customHeight="1" s="48">
+    <row r="83" ht="42" customHeight="1" s="48">
       <c r="B83" s="70">
         <f>+B82+1</f>
         <v/>
@@ -3103,7 +3110,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="36" customHeight="1" s="48">
+    <row r="86" ht="57" customHeight="1" s="48">
       <c r="B86" s="70">
         <f>+B83+1</f>
         <v/>
@@ -3141,7 +3148,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="36" customHeight="1" s="48">
+    <row r="87" ht="57" customHeight="1" s="48">
       <c r="B87" s="70">
         <f>+B86+1</f>
         <v/>
@@ -3179,7 +3186,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="36" customHeight="1" s="48">
+    <row r="88" ht="57" customHeight="1" s="48">
       <c r="B88" s="70">
         <f>+B87+1</f>
         <v/>
@@ -3213,7 +3220,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="36" customHeight="1" s="48">
+    <row r="89" ht="42" customHeight="1" s="48">
       <c r="B89" s="70">
         <f>+B88+1</f>
         <v/>
@@ -3247,7 +3254,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="36" customHeight="1" s="48">
+    <row r="90" ht="42" customHeight="1" s="48">
       <c r="B90" s="70">
         <f>+B89+1</f>
         <v/>
@@ -3281,7 +3288,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="36" customHeight="1" s="48">
+    <row r="91" ht="72" customHeight="1" s="48">
       <c r="B91" s="70">
         <f>+B90+1</f>
         <v/>
@@ -3319,7 +3326,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="36" customHeight="1" s="48">
+    <row r="92" ht="57" customHeight="1" s="48">
       <c r="B92" s="70">
         <f>+B91+1</f>
         <v/>
@@ -3357,7 +3364,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1" s="48">
+    <row r="93" ht="57" customHeight="1" s="48">
       <c r="B93" s="70">
         <f>+B92+1</f>
         <v/>
@@ -3395,7 +3402,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="21" customHeight="1" s="48">
+    <row r="94" ht="42" customHeight="1" s="48">
       <c r="B94" s="70">
         <f>+B93+1</f>
         <v/>
@@ -3433,7 +3440,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="36" customHeight="1" s="48">
+    <row r="95" ht="42" customHeight="1" s="48">
       <c r="B95" s="70">
         <f>+B94+1</f>
         <v/>
@@ -3471,7 +3478,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="21" customHeight="1" s="48">
+    <row r="96" ht="42" customHeight="1" s="48">
       <c r="B96" s="70">
         <f>+B95+1</f>
         <v/>
@@ -3509,7 +3516,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="36" customHeight="1" s="48">
+    <row r="97" ht="57" customHeight="1" s="48">
       <c r="B97" s="70">
         <f>+B96+1</f>
         <v/>
@@ -3547,7 +3554,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="36" customHeight="1" s="48">
+    <row r="98" ht="42" customHeight="1" s="48">
       <c r="B98" s="70">
         <f>+B97+1</f>
         <v/>
@@ -3585,7 +3592,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="36" customHeight="1" s="48">
+    <row r="99" ht="42" customHeight="1" s="48">
       <c r="B99" s="70">
         <f>+B98+1</f>
         <v/>
@@ -3619,7 +3626,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="36" customHeight="1" s="48">
+    <row r="100" ht="57" customHeight="1" s="48">
       <c r="B100" s="70">
         <f>+B99+1</f>
         <v/>
@@ -3663,7 +3670,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="51" customHeight="1" s="48">
+    <row r="103" ht="87" customHeight="1" s="48">
       <c r="B103" s="70">
         <f>+B100+1</f>
         <v/>
@@ -3701,7 +3708,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="36" customHeight="1" s="48">
+    <row r="104" ht="57" customHeight="1" s="48">
       <c r="B104" s="70">
         <f>+B103+1</f>
         <v/>
@@ -3735,7 +3742,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="36" customHeight="1" s="48">
+    <row r="105" ht="42" customHeight="1" s="48">
       <c r="B105" s="70">
         <f>+B104+1</f>
         <v/>
@@ -3773,7 +3780,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="36" customHeight="1" s="48">
+    <row r="106" ht="42" customHeight="1" s="48">
       <c r="B106" s="70">
         <f>+B105+1</f>
         <v/>
@@ -3807,7 +3814,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="36" customHeight="1" s="48">
+    <row r="107" ht="42" customHeight="1" s="48">
       <c r="B107" s="70">
         <f>+B106+1</f>
         <v/>
@@ -3845,7 +3852,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="36" customHeight="1" s="48">
+    <row r="108" ht="42" customHeight="1" s="48">
       <c r="B108" s="70">
         <f>+B107+1</f>
         <v/>
@@ -3883,7 +3890,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="36" customHeight="1" s="48">
+    <row r="109" ht="42" customHeight="1" s="48">
       <c r="B109" s="70">
         <f>+B108+1</f>
         <v/>
@@ -3917,7 +3924,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="36" customHeight="1" s="48">
+    <row r="110" ht="42" customHeight="1" s="48">
       <c r="B110" s="70">
         <f>+B109+1</f>
         <v/>
@@ -3951,7 +3958,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="36" customHeight="1" s="48">
+    <row r="111" ht="42" customHeight="1" s="48">
       <c r="B111" s="70">
         <f>+B110+1</f>
         <v/>
@@ -3995,7 +4002,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="21" customHeight="1" s="48">
+    <row r="114" ht="42" customHeight="1" s="48">
       <c r="B114" s="70">
         <f>+B111+1</f>
         <v/>
@@ -4033,7 +4040,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="36" customHeight="1" s="48">
+    <row r="115" ht="42" customHeight="1" s="48">
       <c r="B115" s="70">
         <f>+B114+1</f>
         <v/>
@@ -4071,7 +4078,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="36" customHeight="1" s="48">
+    <row r="116" ht="42" customHeight="1" s="48">
       <c r="B116" s="70">
         <f>+B115+1</f>
         <v/>
@@ -4109,7 +4116,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="21" customHeight="1" s="48">
+    <row r="117" ht="42" customHeight="1" s="48">
       <c r="B117" s="70">
         <f>+B116+1</f>
         <v/>
@@ -4143,7 +4150,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="36" customHeight="1" s="48">
+    <row r="118" ht="42" customHeight="1" s="48">
       <c r="B118" s="70">
         <f>+B117+1</f>
         <v/>
@@ -4177,7 +4184,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="21" customHeight="1" s="48">
+    <row r="119" ht="42" customHeight="1" s="48">
       <c r="B119" s="70">
         <f>+B118+1</f>
         <v/>
@@ -4211,7 +4218,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="21" customHeight="1" s="48">
+    <row r="120" ht="42" customHeight="1" s="48">
       <c r="B120" s="70">
         <f>+B119+1</f>
         <v/>
@@ -4245,7 +4252,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="36" customHeight="1" s="48">
+    <row r="121" ht="42" customHeight="1" s="48">
       <c r="B121" s="70">
         <f>+B120+1</f>
         <v/>
@@ -4279,7 +4286,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="21" customHeight="1" s="48">
+    <row r="122" ht="42" customHeight="1" s="48">
       <c r="B122" s="70">
         <f>+B121+1</f>
         <v/>
@@ -4317,7 +4324,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="21" customHeight="1" s="48">
+    <row r="123" ht="42" customHeight="1" s="48">
       <c r="B123" s="70">
         <f>+B122+1</f>
         <v/>
@@ -4351,7 +4358,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="21" customHeight="1" s="48">
+    <row r="124" ht="42" customHeight="1" s="48">
       <c r="B124" s="70">
         <f>+B123+1</f>
         <v/>
@@ -4389,7 +4396,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="21" customHeight="1" s="48">
+    <row r="125" ht="42" customHeight="1" s="48">
       <c r="B125" s="70">
         <f>+B124+1</f>
         <v/>
@@ -4437,7 +4444,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="36" customHeight="1" s="48">
+    <row r="128" ht="42" customHeight="1" s="48">
       <c r="B128" s="70">
         <f>+B125+1</f>
         <v/>
@@ -4475,7 +4482,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="21" customHeight="1" s="48">
+    <row r="129" ht="42" customHeight="1" s="48">
       <c r="B129" s="70">
         <f>+B128+1</f>
         <v/>
@@ -4509,7 +4516,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="21" customHeight="1" s="48">
+    <row r="130" ht="42" customHeight="1" s="48">
       <c r="B130" s="70">
         <f>+B129+1</f>
         <v/>
@@ -4543,7 +4550,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="21" customHeight="1" s="48">
+    <row r="131" ht="42" customHeight="1" s="48">
       <c r="B131" s="70">
         <f>+B130+1</f>
         <v/>
@@ -4577,7 +4584,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="21" customHeight="1" s="48">
+    <row r="132" ht="42" customHeight="1" s="48">
       <c r="B132" s="70">
         <f>+B131+1</f>
         <v/>
@@ -4611,7 +4618,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="21" customHeight="1" s="48">
+    <row r="133" ht="42" customHeight="1" s="48">
       <c r="B133" s="70">
         <f>+B132+1</f>
         <v/>
@@ -4649,7 +4656,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="21" customHeight="1" s="48">
+    <row r="134" ht="42" customHeight="1" s="48">
       <c r="B134" s="70">
         <f>+B133+1</f>
         <v/>
@@ -4687,7 +4694,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="21" customHeight="1" s="48">
+    <row r="135" ht="42" customHeight="1" s="48">
       <c r="B135" s="70">
         <f>+B134+1</f>
         <v/>
@@ -4728,7 +4735,7 @@
     <mergeCell ref="C5:M5"/>
     <mergeCell ref="C4:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="M11:M69">
+  <conditionalFormatting sqref="M11:M135">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>"Partiellement Reçu"</formula>
     </cfRule>
@@ -4739,7 +4746,7 @@
       <formula>"Reçu"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E69">
+  <conditionalFormatting sqref="E11:E135">
     <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
       <formula>"Faible"</formula>
     </cfRule>
@@ -4782,7 +4789,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:D9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -4852,7 +4859,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="48">
+    <row r="8" ht="87" customHeight="1" s="48">
       <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Non Reçu</t>
@@ -4868,7 +4875,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" s="48">
+    <row r="9" ht="30" customHeight="1" s="48">
       <c r="B9" s="94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4887,7 +4894,7 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -42148,7 +42155,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:E42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -42195,8 +42202,8 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" s="48">
-      <c r="B6" s="94" t="n">
+    <row r="6" ht="72" customHeight="1" s="48">
+      <c r="B6" s="96" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="95" t="inlineStr">
@@ -42215,8 +42222,8 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="31.5" customHeight="1" s="48">
-      <c r="B7" s="94" t="n">
+    <row r="7" ht="42" customHeight="1" s="48">
+      <c r="B7" s="96" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="95" t="inlineStr">
@@ -42235,8 +42242,8 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45.75" customHeight="1" s="48">
-      <c r="B8" s="94" t="n">
+    <row r="8" ht="57" customHeight="1" s="48">
+      <c r="B8" s="96" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="95" t="inlineStr">
@@ -42255,8 +42262,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="31.5" customHeight="1" s="48">
-      <c r="B9" s="94" t="n">
+    <row r="9" ht="42" customHeight="1" s="48">
+      <c r="B9" s="96" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="95" t="inlineStr">
@@ -42275,8 +42282,8 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45.75" customHeight="1" s="48">
-      <c r="B10" s="94" t="n">
+    <row r="10" ht="57" customHeight="1" s="48">
+      <c r="B10" s="96" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="95" t="inlineStr">
@@ -42295,8 +42302,8 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="31.5" customHeight="1" s="48">
-      <c r="B11" s="94" t="n">
+    <row r="11" ht="42" customHeight="1" s="48">
+      <c r="B11" s="96" t="n">
         <v>6</v>
       </c>
       <c r="C11" s="95" t="inlineStr">
@@ -42315,8 +42322,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="31.5" customHeight="1" s="48">
-      <c r="B12" s="94" t="n">
+    <row r="12" ht="42" customHeight="1" s="48">
+      <c r="B12" s="96" t="n">
         <v>7</v>
       </c>
       <c r="C12" s="95" t="inlineStr">
@@ -42335,8 +42342,8 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="45.75" customHeight="1" s="48">
-      <c r="B13" s="94" t="n">
+    <row r="13" ht="72" customHeight="1" s="48">
+      <c r="B13" s="96" t="n">
         <v>8</v>
       </c>
       <c r="C13" s="95" t="inlineStr">
@@ -42355,8 +42362,8 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="31.5" customHeight="1" s="48">
-      <c r="B14" s="94" t="n">
+    <row r="14" ht="42" customHeight="1" s="48">
+      <c r="B14" s="96" t="n">
         <v>9</v>
       </c>
       <c r="C14" s="95" t="inlineStr">
@@ -42375,8 +42382,8 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="31.5" customHeight="1" s="48">
-      <c r="B15" s="94" t="n">
+    <row r="15" ht="57" customHeight="1" s="48">
+      <c r="B15" s="96" t="n">
         <v>10</v>
       </c>
       <c r="C15" s="95" t="inlineStr">
@@ -42395,8 +42402,8 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" s="48">
-      <c r="B16" s="94" t="n">
+    <row r="16" ht="87" customHeight="1" s="48">
+      <c r="B16" s="96" t="n">
         <v>11</v>
       </c>
       <c r="C16" s="95" t="inlineStr">
@@ -42415,8 +42422,8 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="73.5" customHeight="1" s="48">
-      <c r="B17" s="94" t="n">
+    <row r="17" ht="102" customHeight="1" s="48">
+      <c r="B17" s="96" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="95" t="inlineStr">
@@ -42435,8 +42442,8 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="45.75" customHeight="1" s="48">
-      <c r="B18" s="94" t="n">
+    <row r="18" ht="57" customHeight="1" s="48">
+      <c r="B18" s="96" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="95" t="inlineStr">
@@ -42455,8 +42462,8 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="31.5" customHeight="1" s="48">
-      <c r="B19" s="94" t="n">
+    <row r="19" ht="42" customHeight="1" s="48">
+      <c r="B19" s="96" t="n">
         <v>14</v>
       </c>
       <c r="C19" s="95" t="inlineStr">
@@ -42475,8 +42482,8 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" s="48">
-      <c r="B20" s="94" t="n">
+    <row r="20" ht="87" customHeight="1" s="48">
+      <c r="B20" s="96" t="n">
         <v>15</v>
       </c>
       <c r="C20" s="95" t="inlineStr">
@@ -42495,8 +42502,8 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" s="48">
-      <c r="B21" s="94" t="n">
+    <row r="21" ht="72" customHeight="1" s="48">
+      <c r="B21" s="96" t="n">
         <v>16</v>
       </c>
       <c r="C21" s="95" t="inlineStr">
@@ -42515,8 +42522,8 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="31.5" customHeight="1" s="48">
-      <c r="B22" s="94" t="n">
+    <row r="22" ht="57" customHeight="1" s="48">
+      <c r="B22" s="96" t="n">
         <v>17</v>
       </c>
       <c r="C22" s="95" t="inlineStr">
@@ -42535,8 +42542,8 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="45.75" customHeight="1" s="48">
-      <c r="B23" s="94" t="n">
+    <row r="23" ht="57" customHeight="1" s="48">
+      <c r="B23" s="96" t="n">
         <v>18</v>
       </c>
       <c r="C23" s="95" t="inlineStr">
@@ -42555,8 +42562,8 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1" s="48">
-      <c r="B24" s="94" t="n">
+    <row r="24" ht="42" customHeight="1" s="48">
+      <c r="B24" s="96" t="n">
         <v>19</v>
       </c>
       <c r="C24" s="95" t="inlineStr">
@@ -42575,8 +42582,8 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="31.5" customHeight="1" s="48">
-      <c r="B25" s="94" t="n">
+    <row r="25" ht="57" customHeight="1" s="48">
+      <c r="B25" s="96" t="n">
         <v>20</v>
       </c>
       <c r="C25" s="95" t="inlineStr">
@@ -42595,8 +42602,8 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="31.5" customHeight="1" s="48">
-      <c r="B26" s="94" t="n">
+    <row r="26" ht="42" customHeight="1" s="48">
+      <c r="B26" s="96" t="n">
         <v>21</v>
       </c>
       <c r="C26" s="95" t="inlineStr">
@@ -42615,11 +42622,9 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+    <row r="27" ht="42" customHeight="1" s="48">
+      <c r="B27" s="96" t="n">
+        <v>22</v>
       </c>
       <c r="C27" s="95" t="inlineStr">
         <is>
@@ -42637,11 +42642,9 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="94" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+    <row r="28" ht="42" customHeight="1" s="48">
+      <c r="B28" s="96" t="n">
+        <v>23</v>
       </c>
       <c r="C28" s="95" t="inlineStr">
         <is>
@@ -42659,11 +42662,9 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="94" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+    <row r="29" ht="42" customHeight="1" s="48">
+      <c r="B29" s="96" t="n">
+        <v>24</v>
       </c>
       <c r="C29" s="95" t="inlineStr">
         <is>
@@ -42681,11 +42682,9 @@
         </is>
       </c>
     </row>
-    <row r="30" s="48">
-      <c r="B30" s="94" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+    <row r="30" ht="42" customHeight="1" s="48">
+      <c r="B30" s="96" t="n">
+        <v>25</v>
       </c>
       <c r="C30" s="95" t="inlineStr">
         <is>
@@ -42703,11 +42702,9 @@
         </is>
       </c>
     </row>
-    <row r="31" s="48">
-      <c r="B31" s="94" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+    <row r="31" ht="87" customHeight="1" s="48">
+      <c r="B31" s="96" t="n">
+        <v>26</v>
       </c>
       <c r="C31" s="95" t="inlineStr">
         <is>
@@ -42725,11 +42722,9 @@
         </is>
       </c>
     </row>
-    <row r="32" s="48">
-      <c r="B32" s="94" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+    <row r="32" ht="72" customHeight="1" s="48">
+      <c r="B32" s="96" t="n">
+        <v>27</v>
       </c>
       <c r="C32" s="95" t="inlineStr">
         <is>
@@ -42747,11 +42742,9 @@
         </is>
       </c>
     </row>
-    <row r="33" s="48">
-      <c r="B33" s="94" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+    <row r="33" ht="72" customHeight="1" s="48">
+      <c r="B33" s="96" t="n">
+        <v>28</v>
       </c>
       <c r="C33" s="95" t="inlineStr">
         <is>
@@ -42769,11 +42762,9 @@
         </is>
       </c>
     </row>
-    <row r="34" s="48">
-      <c r="B34" s="94" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+    <row r="34" ht="57" customHeight="1" s="48">
+      <c r="B34" s="96" t="n">
+        <v>29</v>
       </c>
       <c r="C34" s="95" t="inlineStr">
         <is>
@@ -42791,8 +42782,8 @@
         </is>
       </c>
     </row>
-    <row r="35" s="48">
-      <c r="B35" s="94" t="n">
+    <row r="35" ht="57" customHeight="1" s="48">
+      <c r="B35" s="96" t="n">
         <v>30</v>
       </c>
       <c r="C35" s="95" t="inlineStr">
@@ -42811,8 +42802,8 @@
         </is>
       </c>
     </row>
-    <row r="36" s="48">
-      <c r="B36" s="94" t="n">
+    <row r="36" ht="57" customHeight="1" s="48">
+      <c r="B36" s="96" t="n">
         <v>31</v>
       </c>
       <c r="C36" s="95" t="inlineStr">
@@ -42831,8 +42822,8 @@
         </is>
       </c>
     </row>
-    <row r="37" s="48">
-      <c r="B37" s="94" t="n">
+    <row r="37" ht="42" customHeight="1" s="48">
+      <c r="B37" s="96" t="n">
         <v>32</v>
       </c>
       <c r="C37" s="95" t="inlineStr">
@@ -42851,8 +42842,8 @@
         </is>
       </c>
     </row>
-    <row r="38" s="48">
-      <c r="B38" s="94" t="n">
+    <row r="38" ht="57" customHeight="1" s="48">
+      <c r="B38" s="96" t="n">
         <v>33</v>
       </c>
       <c r="C38" s="95" t="inlineStr">
@@ -42871,8 +42862,8 @@
         </is>
       </c>
     </row>
-    <row r="39" s="48">
-      <c r="B39" s="94" t="n">
+    <row r="39" ht="42" customHeight="1" s="48">
+      <c r="B39" s="96" t="n">
         <v>34</v>
       </c>
       <c r="C39" s="95" t="inlineStr">
@@ -42891,8 +42882,8 @@
         </is>
       </c>
     </row>
-    <row r="40" s="48">
-      <c r="B40" s="94" t="n">
+    <row r="40" ht="57" customHeight="1" s="48">
+      <c r="B40" s="96" t="n">
         <v>35</v>
       </c>
       <c r="C40" s="95" t="inlineStr">
@@ -42911,8 +42902,8 @@
         </is>
       </c>
     </row>
-    <row r="41" s="48">
-      <c r="B41" s="94" t="n">
+    <row r="41" ht="42" customHeight="1" s="48">
+      <c r="B41" s="96" t="n">
         <v>36</v>
       </c>
       <c r="C41" s="95" t="inlineStr">
@@ -42931,8 +42922,8 @@
         </is>
       </c>
     </row>
-    <row r="42" s="48">
-      <c r="B42" s="94" t="n">
+    <row r="42" ht="31.5" customHeight="1" s="48">
+      <c r="B42" s="96" t="n">
         <v>37</v>
       </c>
       <c r="C42" s="95" t="inlineStr">
@@ -42954,6 +42945,6 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/FPPN_PBC_complete_pointee_20261019.xlsx
+++ b/FPPN_PBC_complete_pointee_20261019.xlsx
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PBC Actuariat FPPN'!$B$12:$P$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'PBC Actuariat FPPN'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'PBC Actuariat FPPN'!$A$1:$N$136</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'PBC Actuariat FPPN'!$A$1:$N$152</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Synthèse du pointage'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Synthèse du pointage'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Détail par mois'!$B$5:$E$1605</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Points à clarifier'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Points à clarifier'!$A$1:$E$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Points à clarifier'!$A$1:$E$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -936,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:M135"/>
+  <dimension ref="B4:M151"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.18359375" defaultRowHeight="13.5" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.82" customWidth="1" style="44" min="1" max="1"/>
@@ -982,7 +982,7 @@
     </row>
     <row r="7" ht="13.5" customHeight="1" s="48">
       <c r="M7" s="53">
-        <f>IFERROR(COUNTIF($M$11:$M$135,"Reçu")/(COUNTA($M$11:$M$135)-COUNTIF($M$11:$M$135,"Non Applicable")),0)</f>
+        <f>IFERROR(COUNTIF($M$11:$M$151,"Reçu")/(COUNTA($M$11:$M$151)-COUNTIF($M$11:$M$151,"Non Applicable")),0)</f>
         <v/>
       </c>
     </row>
@@ -4723,6 +4723,386 @@
         </is>
       </c>
       <c r="M135" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="136"/>
+    <row r="137" ht="18" customHeight="1" s="48">
+      <c r="C137" s="69" t="inlineStr">
+        <is>
+          <t>Textes du FPPN cités par les statuts et le règlement intérieur (lecture des textes du 15/06/2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1" s="48">
+      <c r="B138" s="70">
+        <f>+B135+1</f>
+        <v/>
+      </c>
+      <c r="C138" s="71" t="inlineStr">
+        <is>
+          <t>Cahier des charges du régime des prestations sociales du FPPN en vigueur, et versions applicables depuis 2020 (cité aux articles 21 et 40 à 42 du règlement intérieur).</t>
+        </is>
+      </c>
+      <c r="E138" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G138" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H138" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I138" s="73" t="n"/>
+      <c r="J138" s="74" t="inlineStr">
+        <is>
+          <t>Physique et Electronique</t>
+        </is>
+      </c>
+      <c r="K138" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M138" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="57" customHeight="1" s="48">
+      <c r="B139" s="70">
+        <f>+B138+1</f>
+        <v/>
+      </c>
+      <c r="C139" s="71" t="inlineStr">
+        <is>
+          <t>Tableau des allocations en vigueur de 2020 au 31/08/2026 : allocation décès du membre, allocation décès des ayants droit, allocation d'invalidité par corps (articles 43, 44, 58 et 59 du règlement intérieur ; complète l'item 93).</t>
+        </is>
+      </c>
+      <c r="E139" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G139" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H139" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I139" s="73" t="n"/>
+      <c r="J139" s="74" t="inlineStr">
+        <is>
+          <t>Physique et Electronique</t>
+        </is>
+      </c>
+      <c r="K139" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M139" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="57" customHeight="1" s="48">
+      <c r="B140" s="70">
+        <f>+B139+1</f>
+        <v/>
+      </c>
+      <c r="C140" s="71" t="inlineStr">
+        <is>
+          <t>Manuels de procédure du Plan Epargne Plus et de l'Entraide de Fin de Carrière : prestations, rémunération servie, conditions de sortie et de rachat (articles 69 et 71 du règlement intérieur).</t>
+        </is>
+      </c>
+      <c r="E140" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G140" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H140" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I140" s="73" t="n"/>
+      <c r="J140" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K140" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M140" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="141"/>
+    <row r="142" ht="18" customHeight="1" s="48">
+      <c r="C142" s="69" t="inlineStr">
+        <is>
+          <t>Personnel de la Direction Générale (périmètre de la provision pour départ à la retraite) (lecture des textes du 15/06/2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="57" customHeight="1" s="48">
+      <c r="B143" s="70">
+        <f>+B140+1</f>
+        <v/>
+      </c>
+      <c r="C143" s="71" t="inlineStr">
+        <is>
+          <t>Fichier du personnel de la Direction Générale avec une colonne de statut : personnel civil salarié ou fonctionnaire de police en service (article 31 du règlement intérieur ; complète l'item 76).</t>
+        </is>
+      </c>
+      <c r="E143" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G143" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H143" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I143" s="73" t="n"/>
+      <c r="J143" s="74" t="inlineStr">
+        <is>
+          <t>Electronique</t>
+        </is>
+      </c>
+      <c r="K143" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M143" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1" s="48">
+      <c r="B144" s="70">
+        <f>+B143+1</f>
+        <v/>
+      </c>
+      <c r="C144" s="71" t="inlineStr">
+        <is>
+          <t>Contrat de travail type du personnel civil, convention collective appliquée et tout avenant fixant l'âge de départ à la retraite (complète l'item 77).</t>
+        </is>
+      </c>
+      <c r="E144" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G144" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H144" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I144" s="73" t="n"/>
+      <c r="J144" s="74" t="n"/>
+      <c r="K144" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M144" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="145"/>
+    <row r="146" ht="18" customHeight="1" s="48">
+      <c r="C146" s="69" t="inlineStr">
+        <is>
+          <t>Décisions des organes (lecture des textes du 15/06/2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="57" customHeight="1" s="48">
+      <c r="B147" s="70">
+        <f>+B144+1</f>
+        <v/>
+      </c>
+      <c r="C147" s="71" t="inlineStr">
+        <is>
+          <t>Délibérations du Conseil d'Administration autorisant les placements et les ouvertures de comptes (DAT BOA, DAT Orabank, FCP géré par United Capital), comme l'exige l'article 85 des statuts.</t>
+        </is>
+      </c>
+      <c r="E147" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G147" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H147" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I147" s="73" t="n"/>
+      <c r="J147" s="74" t="n"/>
+      <c r="K147" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M147" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1" s="48">
+      <c r="B148" s="70">
+        <f>+B147+1</f>
+        <v/>
+      </c>
+      <c r="C148" s="71" t="inlineStr">
+        <is>
+          <t>Procès-verbal de l'Assemblée Générale approuvant le reclassement des provisions techniques en comptes 15801000 et 15802000 en 2024 (article 75 des statuts).</t>
+        </is>
+      </c>
+      <c r="E148" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G148" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H148" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I148" s="73" t="n"/>
+      <c r="J148" s="74" t="n"/>
+      <c r="K148" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M148" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1" s="48">
+      <c r="B149" s="70">
+        <f>+B148+1</f>
+        <v/>
+      </c>
+      <c r="C149" s="71" t="inlineStr">
+        <is>
+          <t>Procès-verbaux des Assemblées Générales d'affectation des résultats de 2020 à 2025 (article 90 des statuts : réserve légale de 20 % à 50 % de l'excédent net).</t>
+        </is>
+      </c>
+      <c r="E149" s="72" t="inlineStr">
+        <is>
+          <t>Moyen</t>
+        </is>
+      </c>
+      <c r="G149" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H149" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I149" s="73" t="n"/>
+      <c r="J149" s="74" t="n"/>
+      <c r="K149" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M149" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="57" customHeight="1" s="48">
+      <c r="B150" s="70">
+        <f>+B149+1</f>
+        <v/>
+      </c>
+      <c r="C150" s="71" t="inlineStr">
+        <is>
+          <t>Décision fixant la situation des policiers retraités : maintien de la qualité de membre (article 7 des statuts), restitution de la carte (article 38 du règlement intérieur), cotisation et garantie santé (complète l'item 79).</t>
+        </is>
+      </c>
+      <c r="E150" s="72" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="G150" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H150" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I150" s="73" t="n"/>
+      <c r="J150" s="74" t="n"/>
+      <c r="K150" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M150" s="76" t="inlineStr">
+        <is>
+          <t>Non Reçu</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="57" customHeight="1" s="48">
+      <c r="B151" s="70">
+        <f>+B150+1</f>
+        <v/>
+      </c>
+      <c r="C151" s="71" t="inlineStr">
+        <is>
+          <t>Délibération du Conseil d'Administration approuvant le cadre organique des emplois de la Direction Générale et la grille des salaires et indemnités (articles 61 et 66 des statuts).</t>
+        </is>
+      </c>
+      <c r="E151" s="72" t="inlineStr">
+        <is>
+          <t>Faible</t>
+        </is>
+      </c>
+      <c r="G151" s="73" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H151" s="73" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I151" s="73" t="n"/>
+      <c r="J151" s="74" t="n"/>
+      <c r="K151" s="75" t="inlineStr">
+        <is>
+          <t>Demande issue de la lecture des statuts et du règlement intérieur du 15/06/2023 (PBC complémentaire textes et personnel).</t>
+        </is>
+      </c>
+      <c r="M151" s="76" t="inlineStr">
         <is>
           <t>Non Reçu</t>
         </is>
@@ -4735,7 +5115,7 @@
     <mergeCell ref="C5:M5"/>
     <mergeCell ref="C4:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="M11:M135">
+  <conditionalFormatting sqref="M11:M151">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>"Partiellement Reçu"</formula>
     </cfRule>
@@ -4746,7 +5126,7 @@
       <formula>"Reçu"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E135">
+  <conditionalFormatting sqref="E11:E151">
     <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
       <formula>"Faible"</formula>
     </cfRule>
@@ -4758,15 +5138,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E11:E135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="E11:E151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Urgent,Moyen,Faible"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="J11:J135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J11:J151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Physique,Electronique,Physique et Electronique"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="M11:M135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="M11:M151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Reçu,Non Reçu,Non Applicable,Partiellement Reçu"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4838,7 +5218,7 @@
         </is>
       </c>
       <c r="C6" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$135,"Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$151,"Reçu")</f>
         <v/>
       </c>
       <c r="D6" s="95" t="n"/>
@@ -4850,7 +5230,7 @@
         </is>
       </c>
       <c r="C7" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$135,"Partiellement Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$151,"Partiellement Reçu")</f>
         <v/>
       </c>
       <c r="D7" s="95" t="inlineStr">
@@ -4859,19 +5239,19 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="87" customHeight="1" s="48">
+    <row r="8" ht="102" customHeight="1" s="48">
       <c r="B8" s="94" t="inlineStr">
         <is>
           <t>Non Reçu</t>
         </is>
       </c>
       <c r="C8" s="95">
-        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$135,"Non Reçu")</f>
+        <f>COUNTIF('PBC Actuariat FPPN'!$M$11:$M$151,"Non Reçu")</f>
         <v/>
       </c>
       <c r="D8" s="95" t="inlineStr">
         <is>
-          <t>1, 2, 5, 7, 8, 10, 11, 13, 14, 15, 16, 18, 19, 20, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 38, 39, 40, 41, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99</t>
+          <t>1, 2, 5, 7, 8, 10, 11, 13, 14, 15, 16, 18, 19, 20, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 38, 39, 40, 41, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99, 100, 101, 102, 103, 104, 105, 106, 107, 108, 109</t>
         </is>
       </c>
     </row>
@@ -4887,7 +5267,7 @@
       </c>
       <c r="D9" s="95" t="inlineStr">
         <is>
-          <t>1 à 99</t>
+          <t>1 à 109</t>
         </is>
       </c>
     </row>
@@ -42157,7 +42537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E42"/>
+  <dimension ref="B2:E46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="2" customWidth="1" style="77" min="1" max="1"/>
@@ -42942,6 +43322,86 @@
         </is>
       </c>
     </row>
+    <row r="43" ht="87" customHeight="1" s="48">
+      <c r="B43" s="96" t="n">
+        <v>38</v>
+      </c>
+      <c r="C43" s="95" t="inlineStr">
+        <is>
+          <t>Policiers retraités</t>
+        </is>
+      </c>
+      <c r="D43" s="95" t="inlineStr">
+        <is>
+          <t>Les statuts (art. 7) font du policier retraité un membre participant, mais le règlement intérieur (art. 38) lui fait restituer sa carte au départ à la retraite, et seule la cotisation du policier en activité est prévue (statuts, art. 80).</t>
+        </is>
+      </c>
+      <c r="E43" s="95" t="inlineStr">
+        <is>
+          <t>Préciser la situation des retraités (item 108).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="57" customHeight="1" s="48">
+      <c r="B44" s="96" t="n">
+        <v>39</v>
+      </c>
+      <c r="C44" s="95" t="inlineStr">
+        <is>
+          <t>Réserve légale 2023</t>
+        </is>
+      </c>
+      <c r="D44" s="95" t="inlineStr">
+        <is>
+          <t>La dotation à la réserve légale de 2023 vaut 8,94 % de l'excédent de 2022, sous le minimum de 20 % de l'article 90 des statuts.</t>
+        </is>
+      </c>
+      <c r="E44" s="95" t="inlineStr">
+        <is>
+          <t>Transmettre le procès-verbal d'affectation (item 107).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="87" customHeight="1" s="48">
+      <c r="B45" s="96" t="n">
+        <v>40</v>
+      </c>
+      <c r="C45" s="95" t="inlineStr">
+        <is>
+          <t>Personnel de la Direction Générale</t>
+        </is>
+      </c>
+      <c r="D45" s="95" t="inlineStr">
+        <is>
+          <t>Deux catégories : personnel civil salarié et fonctionnaires de police percevant des indemnités (règlement intérieur, art. 31). Seul le personnel civil relève a priori de l'indemnité de départ du décret n° 2017-210.</t>
+        </is>
+      </c>
+      <c r="E45" s="95" t="inlineStr">
+        <is>
+          <t>Transmettre le fichier du personnel avec le statut (item 103).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="57" customHeight="1" s="48">
+      <c r="B46" s="96" t="n">
+        <v>41</v>
+      </c>
+      <c r="C46" s="95" t="inlineStr">
+        <is>
+          <t>Cahier des charges</t>
+        </is>
+      </c>
+      <c r="D46" s="95" t="inlineStr">
+        <is>
+          <t>Les montants des prestations, de l'EFC et du PEP sont renvoyés au cahier des charges et au tableau des allocations, non transmis.</t>
+        </is>
+      </c>
+      <c r="E46" s="95" t="inlineStr">
+        <is>
+          <t>Transmettre les deux documents (items 100 et 101).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
